--- a/packages/calculators/src/modules/test/6.1-crop-residues.xlsx
+++ b/packages/calculators/src/modules/test/6.1-crop-residues.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A3B490-CB30-6141-A934-B7F7116D901B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2393B0D-E024-114F-AA9D-6F037E3E6E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="600" windowWidth="28800" windowHeight="15940" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15940" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="6.1.1.1" sheetId="1" r:id="rId1"/>
@@ -478,9 +478,6 @@
     <t>Pc</t>
   </si>
   <si>
-    <t>Area sown hectares</t>
-  </si>
-  <si>
     <t>Sugar cane</t>
   </si>
   <si>
@@ -511,7 +508,7 @@
     <t>Peanuts</t>
   </si>
   <si>
-    <t>Hops</t>
+    <t>Hops and grape vines</t>
   </si>
   <si>
     <t>Oilseeds</t>
@@ -568,7 +565,10 @@
     <t>Custom values</t>
   </si>
   <si>
-    <t>Average yield per hectare in t</t>
+    <t>Total yield in kg</t>
+  </si>
+  <si>
+    <t>Mremoved</t>
   </si>
 </sst>
 </file>
@@ -662,7 +662,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -684,6 +684,7 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf applyFill="1" numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1018,70 +1019,71 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78A5655F-5BFE-554E-A3D3-9DFA9517010F}">
-  <dimension ref="A1:AB58"/>
+  <dimension ref="A1:AA58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="11.83203125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" customWidth="1"/>
     <col min="3" max="3" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1640625" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.83203125" customWidth="1"/>
-    <col min="14" max="14" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="12.83203125" customWidth="1"/>
-    <col min="18" max="18" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="36" customWidth="1"/>
-    <col min="24" max="24" width="6.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.1640625" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.83203125" customWidth="1"/>
+    <col min="13" max="13" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" customWidth="1"/>
+    <col min="17" max="17" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="36" customWidth="1"/>
+    <col min="23" max="23" width="6.33203125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="17">
+    <row r="1" spans="1:21" ht="17">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
-      <c r="P2" s="1"/>
-      <c r="R2" s="1"/>
-    </row>
-    <row r="3" spans="1:22" ht="34">
+    <row r="2" spans="1:21">
+      <c r="O2" s="1"/>
+      <c r="Q2" s="1"/>
+    </row>
+    <row r="3" spans="1:21" ht="34">
+      <c r="D3" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="8"/>
       <c r="F3" s="8" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="H3" s="8"/>
       <c r="I3" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>66</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>69</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="L3" s="8" t="s">
-        <v>68</v>
-      </c>
+      <c r="L3" s="8"/>
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="1"/>
-    </row>
-    <row r="4" spans="1:22" ht="17">
+      <c r="Q3" s="1"/>
+    </row>
+    <row r="4" spans="1:21" ht="17">
       <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
@@ -1092,49 +1094,46 @@
         <v>28</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="F4" t="s">
         <v>29</v>
       </c>
+      <c r="G4" t="s" s="15">
+        <v>41</v>
+      </c>
       <c r="H4" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" t="s">
         <v>21</v>
       </c>
-      <c r="N4" t="s">
+      <c r="M4" t="s">
         <v>40</v>
       </c>
+      <c r="O4" t="s">
+        <v>13</v>
+      </c>
       <c r="P4" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q4" t="s">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="Q4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="T4" s="7" t="s">
+      <c r="S4" s="7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:21">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1144,65 +1143,59 @@
       <c r="C5" t="s">
         <v>34</v>
       </c>
-      <c r="D5">
-        <v>50</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5" s="14">
+      <c r="D5" s="14">
         <v>0.2</v>
       </c>
-      <c r="G5" s="14" cm="1">
-        <f t="array" ref="G5">_xlfn.IFS(ISBLANK(A5), "",B5="Sugar Cane", VLOOKUP(C5, $U$48:$V$50, 2, FALSE),_xlfn.IFNA(MATCH(B5, $T$43:$T$47, 0), FALSE), VLOOKUP(B5, $T$43:$V$47, 3, FALSE), TRUE, VLOOKUP(C5, $U$51:$V$53, 2, FALSE))</f>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14" cm="1">
+        <f t="array" ref="F5">_xlfn.IFS(ISBLANK(A5), "",B5="Sugar Cane", VLOOKUP(C5, $T$48:$U$50, 2, FALSE),_xlfn.IFNA(MATCH(B5, $S$43:$S$47, 0), FALSE), VLOOKUP(B5, $S$43:$U$47, 3, FALSE), TRUE, VLOOKUP(C5, $T$51:$U$53, 2, FALSE))</f>
         <v>0</v>
       </c>
+      <c r="G5" s="14">
+        <v>1000</v>
+      </c>
       <c r="H5" s="14">
-        <f>IF(ISBLANK(A5), "", D5*(E5 * 1000))</f>
-        <v>100000</v>
+        <f t="shared" ref="H5:H14" si="0">IF(ISBLANK($A5), "", VLOOKUP($B5, $S$22:$AA$39, 2, FALSE))</f>
+        <v>0.25</v>
       </c>
       <c r="I5" s="14">
-        <f t="shared" ref="I5:I14" si="0">IF(ISBLANK($A5), "", VLOOKUP($B5, $T$22:$AB$39, 2, FALSE))</f>
-        <v>0.25</v>
+        <f t="shared" ref="I5:I14" si="1">IF(ISBLANK($A5), "", VLOOKUP($B5, $S$22:$AA$39, 3, FALSE))</f>
+        <v>0.45</v>
       </c>
       <c r="J5" s="14">
-        <f t="shared" ref="J5:J14" si="1">IF(ISBLANK($A5), "", VLOOKUP($B5, $T$22:$AB$39, 3, FALSE))</f>
-        <v>0.45</v>
+        <f t="shared" ref="J5:J14" si="2">IF(ISBLANK($A5), "", VLOOKUP($B5, $S$22:$AA$39, 4, FALSE))</f>
+        <v>0.2</v>
       </c>
       <c r="K5" s="14">
-        <f t="shared" ref="K5:K14" si="2">IF(ISBLANK($A5), "", VLOOKUP($B5, $T$22:$AB$39, 4, FALSE))</f>
-        <v>0.2</v>
+        <f t="shared" ref="K5:K14" si="3">IF(ISBLANK($A5), "", VLOOKUP($B5, $S$22:$AA$39, 6, FALSE))</f>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="L5" s="14">
-        <f t="shared" ref="L5:L14" si="3">IF(ISBLANK($A5), "", VLOOKUP($B5, $T$22:$AB$39, 6, FALSE))</f>
+        <f>IF(K5="n/a",0,K5)</f>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="M5" s="14">
-        <f>IF(L5="n/a",0,L5)</f>
-        <v>5.0000000000000001E-3</v>
+        <f t="shared" ref="M5:M20" si="4">IF(ISBLANK($A5), "", VLOOKUP($B5, $S$22:$AA$39, 7, FALSE))</f>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="N5" s="14">
-        <f>IF(ISBLANK($A5), "", VLOOKUP($B5, $T$22:$AB$39, 7, FALSE))</f>
+        <f>IF(M5="n/a",0,M5)</f>
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="O5" s="14">
-        <f>IF(N5="n/a",0,N5)</f>
-        <v>7.0000000000000001E-3</v>
+      <c r="O5">
+        <f t="shared" ref="O5:O14" si="5">IF(ISBLANK(A5),"", (G5*H5*(1 - D5 - F5) * J5*L5)+(G5*H5*I5*J5*N5))</f>
+        <v>0.35750000000000004</v>
       </c>
       <c r="P5">
-        <f t="shared" ref="P5:P14" si="4">IF(ISBLANK(A5),"", (H5*I5*(1 - F5 - G5) * K5*M5)+(H5*I5*J5*K5*O5))</f>
-        <v>35.75</v>
+        <f t="shared" ref="P5:P14" si="6">IF(ISBLANK(A5),"",VLOOKUP(A5,$S$14:$T$30,2,FALSE))</f>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="Q5">
-        <f t="shared" ref="Q5:Q14" si="5">IF(ISBLANK(A5),"",VLOOKUP(A5,$T$14:$U$30,2,FALSE))</f>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="R5">
-        <f t="shared" ref="R5:R14" si="6">IF(ISBLANK(A5), "", P5*Q5*$U$10/1000)</f>
-        <v>3.370714285714286E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22">
+        <f t="shared" ref="Q5:Q14" si="7">IF(ISBLANK(A5), "", O5*P5*$T$10/1000)</f>
+        <v>3.3707142857142858E-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -1213,64 +1206,57 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>50</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
         <v>0.2</v>
       </c>
-      <c r="G6" cm="1">
-        <f t="array" ref="G6">_xlfn.IFS(ISBLANK(A6), "",B6="Sugar Cane", VLOOKUP(C6, $U$48:$V$50, 2, FALSE),_xlfn.IFNA(MATCH(B6, $T$43:$T$47, 0), FALSE), VLOOKUP(B6, $T$43:$V$47, 3, FALSE), TRUE, VLOOKUP(C6, $U$51:$V$53, 2, FALSE))</f>
+      <c r="F6" cm="1">
+        <f t="array" ref="F6">_xlfn.IFS(ISBLANK(A6), "",B6="Sugar Cane", VLOOKUP(C6, $T$48:$U$50, 2, FALSE),_xlfn.IFNA(MATCH(B6, $S$43:$S$47, 0), FALSE), VLOOKUP(B6, $S$43:$U$47, 3, FALSE), TRUE, VLOOKUP(C6, $T$51:$U$53, 2, FALSE))</f>
         <v>0</v>
       </c>
+      <c r="G6" s="14">
+        <v>1100</v>
+      </c>
       <c r="H6" s="14">
-        <f t="shared" ref="H6:H20" si="7">IF(ISBLANK(A6), "", D6*(E6 * 1000))</f>
-        <v>100000</v>
-      </c>
-      <c r="I6" s="14">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="J6" s="14">
+      <c r="I6" s="14">
         <f t="shared" si="1"/>
         <v>0.45</v>
       </c>
-      <c r="K6" s="14">
+      <c r="J6" s="14">
         <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
-      <c r="L6" s="14">
+      <c r="K6" s="14">
         <f t="shared" si="3"/>
         <v>5.0000000000000001E-3</v>
       </c>
+      <c r="L6" s="14">
+        <f t="shared" ref="L6:L20" si="8">IF(K6="n/a",0,K6)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
       <c r="M6" s="14">
-        <f t="shared" ref="M6:M20" si="8">IF(L6="n/a",0,L6)</f>
+        <f t="shared" si="4"/>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="N6">
+        <f t="shared" ref="N6:N20" si="9">IF(M6="n/a",0,M6)</f>
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="5"/>
+        <v>0.39324999999999999</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="6"/>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="N6" s="14">
-        <f t="shared" ref="N6:N20" si="9">IF(ISBLANK($A6), "", VLOOKUP($B6, $T$22:$AB$39, 7, FALSE))</f>
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="O6">
-        <f t="shared" ref="O6:O20" si="10">IF(N6="n/a",0,N6)</f>
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="P6">
-        <f t="shared" si="4"/>
-        <v>35.75</v>
-      </c>
       <c r="Q6">
-        <f t="shared" si="5"/>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="6"/>
-        <v>2.8089285714285711E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22">
+        <f t="shared" si="7"/>
+        <v>3.0898214285714286E-6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -1281,64 +1267,57 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>50</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
         <v>0.2</v>
       </c>
-      <c r="G7" cm="1">
-        <f t="array" ref="G7">_xlfn.IFS(ISBLANK(A7), "",B7="Sugar Cane", VLOOKUP(C7, $U$48:$V$50, 2, FALSE),_xlfn.IFNA(MATCH(B7, $T$43:$T$47, 0), FALSE), VLOOKUP(B7, $T$43:$V$47, 3, FALSE), TRUE, VLOOKUP(C7, $U$51:$V$53, 2, FALSE))</f>
+      <c r="F7" cm="1">
+        <f t="array" ref="F7">_xlfn.IFS(ISBLANK(A7), "",B7="Sugar Cane", VLOOKUP(C7, $T$48:$U$50, 2, FALSE),_xlfn.IFNA(MATCH(B7, $S$43:$S$47, 0), FALSE), VLOOKUP(B7, $S$43:$U$47, 3, FALSE), TRUE, VLOOKUP(C7, $T$51:$U$53, 2, FALSE))</f>
         <v>0.06</v>
       </c>
+      <c r="G7" s="14">
+        <v>1200</v>
+      </c>
       <c r="H7" s="14">
-        <f t="shared" si="7"/>
-        <v>100000</v>
-      </c>
-      <c r="I7" s="14">
         <f t="shared" si="0"/>
         <v>1.31</v>
       </c>
-      <c r="J7" s="14">
+      <c r="I7" s="14">
         <f t="shared" si="1"/>
         <v>0.16</v>
       </c>
-      <c r="K7" s="14">
+      <c r="J7" s="14">
         <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
-      <c r="L7" s="14">
+      <c r="K7" s="14">
         <f t="shared" si="3"/>
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="M7" s="14">
+      <c r="L7" s="14">
         <f t="shared" si="8"/>
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="N7" s="14">
+      <c r="M7" s="14">
+        <f t="shared" si="4"/>
+        <v>0.01</v>
+      </c>
+      <c r="N7">
         <f t="shared" si="9"/>
         <v>0.01</v>
       </c>
       <c r="O7">
-        <f t="shared" si="10"/>
-        <v>0.01</v>
+        <f t="shared" si="5"/>
+        <v>8.5265280000000008</v>
       </c>
       <c r="P7">
-        <f t="shared" si="4"/>
-        <v>710.5440000000001</v>
+        <f t="shared" si="6"/>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="5"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="6"/>
-        <v>6.6994148571428583E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22">
+        <f t="shared" si="7"/>
+        <v>8.039297828571429E-5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -1349,211 +1328,190 @@
         <v>37</v>
       </c>
       <c r="D8">
-        <v>50</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="F8">
         <v>0.2</v>
       </c>
-      <c r="G8" cm="1">
-        <f t="array" ref="G8">_xlfn.IFS(ISBLANK(A8), "",B8="Sugar Cane", VLOOKUP(C8, $U$48:$V$50, 2, FALSE),_xlfn.IFNA(MATCH(B8, $T$43:$T$47, 0), FALSE), VLOOKUP(B8, $T$43:$V$47, 3, FALSE), TRUE, VLOOKUP(C8, $U$51:$V$53, 2, FALSE))</f>
+      <c r="F8" cm="1">
+        <f t="array" ref="F8">_xlfn.IFS(ISBLANK(A8), "",B8="Sugar Cane", VLOOKUP(C8, $T$48:$U$50, 2, FALSE),_xlfn.IFNA(MATCH(B8, $S$43:$S$47, 0), FALSE), VLOOKUP(B8, $S$43:$U$47, 3, FALSE), TRUE, VLOOKUP(C8, $T$51:$U$53, 2, FALSE))</f>
         <v>0.06</v>
       </c>
+      <c r="G8" s="14">
+        <v>1300</v>
+      </c>
       <c r="H8" s="14">
-        <f t="shared" si="7"/>
-        <v>100000</v>
-      </c>
-      <c r="I8" s="14">
         <f t="shared" si="0"/>
         <v>1.31</v>
       </c>
-      <c r="J8" s="14">
+      <c r="I8" s="14">
         <f t="shared" si="1"/>
         <v>0.16</v>
       </c>
-      <c r="K8" s="14">
+      <c r="J8" s="14">
         <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
-      <c r="L8" s="14">
+      <c r="K8" s="14">
         <f t="shared" si="3"/>
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="M8" s="14">
+      <c r="L8" s="14">
         <f t="shared" si="8"/>
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="N8" s="14">
+      <c r="M8" s="14">
+        <f t="shared" si="4"/>
+        <v>0.01</v>
+      </c>
+      <c r="N8">
         <f t="shared" si="9"/>
         <v>0.01</v>
       </c>
       <c r="O8">
-        <f t="shared" si="10"/>
-        <v>0.01</v>
+        <f t="shared" si="5"/>
+        <v>9.2370720000000013</v>
       </c>
       <c r="P8">
-        <f t="shared" si="4"/>
-        <v>710.5440000000001</v>
+        <f t="shared" si="6"/>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="5"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="6"/>
-        <v>6.6994148571428583E-3</v>
-      </c>
+        <f t="shared" si="7"/>
+        <v>8.7092393142857149E-5</v>
+      </c>
+      <c r="S8" s="2"/>
       <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-    </row>
-    <row r="9" spans="1:22">
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D9">
-        <v>50</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9">
         <v>0.2</v>
       </c>
-      <c r="G9" cm="1">
-        <f t="array" ref="G9">_xlfn.IFS(ISBLANK(A9), "",B9="Sugar Cane", VLOOKUP(C9, $U$48:$V$50, 2, FALSE),_xlfn.IFNA(MATCH(B9, $T$43:$T$47, 0), FALSE), VLOOKUP(B9, $T$43:$V$47, 3, FALSE), TRUE, VLOOKUP(C9, $U$51:$V$53, 2, FALSE))</f>
+      <c r="F9" cm="1">
+        <f t="array" ref="F9">_xlfn.IFS(ISBLANK(A9), "",B9="Sugar Cane", VLOOKUP(C9, $T$48:$U$50, 2, FALSE),_xlfn.IFNA(MATCH(B9, $S$43:$S$47, 0), FALSE), VLOOKUP(B9, $S$43:$U$47, 3, FALSE), TRUE, VLOOKUP(C9, $T$51:$U$53, 2, FALSE))</f>
         <v>1</v>
       </c>
+      <c r="G9" s="14">
+        <v>1400</v>
+      </c>
       <c r="H9" s="14">
-        <f t="shared" si="7"/>
-        <v>100000</v>
-      </c>
-      <c r="I9" s="14">
         <f t="shared" si="0"/>
         <v>0.34</v>
       </c>
-      <c r="J9" s="14">
+      <c r="I9" s="14">
         <f t="shared" si="1"/>
         <v>0.43</v>
       </c>
-      <c r="K9" s="14">
+      <c r="J9" s="14">
         <f t="shared" si="2"/>
         <v>0.25</v>
       </c>
-      <c r="L9" s="14">
+      <c r="K9" s="14">
         <f t="shared" si="3"/>
         <v>0.02</v>
       </c>
-      <c r="M9" s="14">
+      <c r="L9" s="14">
         <f t="shared" si="8"/>
         <v>0.02</v>
       </c>
-      <c r="N9" s="14">
+      <c r="M9" s="14">
+        <f t="shared" si="4"/>
+        <v>0.01</v>
+      </c>
+      <c r="N9">
         <f t="shared" si="9"/>
         <v>0.01</v>
       </c>
       <c r="O9">
-        <f t="shared" si="10"/>
-        <v>0.01</v>
+        <f t="shared" si="5"/>
+        <v>3.5700000000000065E-2</v>
       </c>
       <c r="P9">
-        <f t="shared" si="4"/>
-        <v>2.5500000000000114</v>
+        <f t="shared" si="6"/>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="5"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="6"/>
-        <v>2.4042857142857252E-5</v>
-      </c>
+        <f t="shared" si="7"/>
+        <v>3.3660000000000062E-7</v>
+      </c>
+      <c r="S9" s="2"/>
       <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-    </row>
-    <row r="10" spans="1:22">
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D10">
-        <v>50</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10">
         <v>0.3</v>
       </c>
-      <c r="G10" cm="1">
-        <f t="array" ref="G10">_xlfn.IFS(ISBLANK(A10), "",B10="Sugar Cane", VLOOKUP(C10, $U$48:$V$50, 2, FALSE),_xlfn.IFNA(MATCH(B10, $T$43:$T$47, 0), FALSE), VLOOKUP(B10, $T$43:$V$47, 3, FALSE), TRUE, VLOOKUP(C10, $U$51:$V$53, 2, FALSE))</f>
+      <c r="F10" cm="1">
+        <f t="array" ref="F10">_xlfn.IFS(ISBLANK(A10), "",B10="Sugar Cane", VLOOKUP(C10, $T$48:$U$50, 2, FALSE),_xlfn.IFNA(MATCH(B10, $S$43:$S$47, 0), FALSE), VLOOKUP(B10, $S$43:$U$47, 3, FALSE), TRUE, VLOOKUP(C10, $T$51:$U$53, 2, FALSE))</f>
         <v>1</v>
       </c>
+      <c r="G10" s="14">
+        <v>1500</v>
+      </c>
       <c r="H10" s="14">
-        <f t="shared" si="7"/>
-        <v>100000</v>
-      </c>
-      <c r="I10" s="14">
         <f t="shared" si="0"/>
         <v>0.34</v>
       </c>
-      <c r="J10" s="14">
+      <c r="I10" s="14">
         <f t="shared" si="1"/>
         <v>0.43</v>
       </c>
-      <c r="K10" s="14">
+      <c r="J10" s="14">
         <f t="shared" si="2"/>
         <v>0.25</v>
       </c>
-      <c r="L10" s="14">
+      <c r="K10" s="14">
         <f t="shared" si="3"/>
         <v>0.02</v>
       </c>
-      <c r="M10" s="14">
+      <c r="L10" s="14">
         <f t="shared" si="8"/>
         <v>0.02</v>
       </c>
-      <c r="N10" s="14">
+      <c r="M10" s="14">
+        <f t="shared" si="4"/>
+        <v>0.01</v>
+      </c>
+      <c r="N10">
         <f t="shared" si="9"/>
         <v>0.01</v>
       </c>
       <c r="O10">
-        <f t="shared" si="10"/>
-        <v>0.01</v>
+        <f t="shared" si="5"/>
+        <v>-0.21675000000000011</v>
       </c>
       <c r="P10">
-        <f t="shared" si="4"/>
-        <v>-14.450000000000003</v>
+        <f t="shared" si="6"/>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="5"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="R10">
-        <f t="shared" si="6"/>
-        <v>-1.3624285714285717E-4</v>
-      </c>
-      <c r="T10" t="s">
+        <f t="shared" si="7"/>
+        <v>-2.0436428571428582E-6</v>
+      </c>
+      <c r="S10" t="s">
         <v>2</v>
       </c>
-      <c r="U10">
+      <c r="T10">
         <f>44/28</f>
         <v>1.5714285714285714</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:21">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -1561,340 +1519,306 @@
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D11">
-        <v>50</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="F11">
         <v>0.3</v>
       </c>
-      <c r="G11" cm="1">
-        <f t="array" ref="G11">_xlfn.IFS(ISBLANK(A11), "",B11="Sugar Cane", VLOOKUP(C11, $U$48:$V$50, 2, FALSE),_xlfn.IFNA(MATCH(B11, $T$43:$T$47, 0), FALSE), VLOOKUP(B11, $T$43:$V$47, 3, FALSE), TRUE, VLOOKUP(C11, $U$51:$V$53, 2, FALSE))</f>
+      <c r="F11" cm="1">
+        <f t="array" ref="F11">_xlfn.IFS(ISBLANK(A11), "",B11="Sugar Cane", VLOOKUP(C11, $T$48:$U$50, 2, FALSE),_xlfn.IFNA(MATCH(B11, $S$43:$S$47, 0), FALSE), VLOOKUP(B11, $S$43:$U$47, 3, FALSE), TRUE, VLOOKUP(C11, $T$51:$U$53, 2, FALSE))</f>
         <v>0</v>
       </c>
+      <c r="G11" s="14">
+        <v>1600</v>
+      </c>
       <c r="H11" s="14">
-        <f t="shared" si="7"/>
-        <v>100000</v>
-      </c>
-      <c r="I11" s="14">
         <f t="shared" si="0"/>
         <v>1.9</v>
       </c>
-      <c r="J11" s="14">
+      <c r="I11" s="14">
         <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
-      <c r="K11" s="14">
+      <c r="J11" s="14">
         <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
+      <c r="K11" s="14">
+        <f t="shared" si="3"/>
+        <v>0.01</v>
+      </c>
       <c r="L11" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>0.01</v>
       </c>
       <c r="M11" s="14">
-        <f t="shared" si="8"/>
-        <v>0.01</v>
-      </c>
-      <c r="N11" s="14">
+        <f t="shared" si="4"/>
+        <v>0.01</v>
+      </c>
+      <c r="N11">
         <f t="shared" si="9"/>
         <v>0.01</v>
       </c>
       <c r="O11">
-        <f t="shared" si="10"/>
-        <v>0.01</v>
+        <f t="shared" si="5"/>
+        <v>27.36</v>
       </c>
       <c r="P11">
-        <f t="shared" si="4"/>
-        <v>1710</v>
+        <f t="shared" si="6"/>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="5"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="6"/>
-        <v>1.6122857142857144E-2</v>
-      </c>
+        <f t="shared" si="7"/>
+        <v>2.5796571428571432E-4</v>
+      </c>
+      <c r="S11" s="2"/>
       <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-    </row>
-    <row r="12" spans="1:22">
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D12">
-        <v>50</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="F12">
         <v>0.3</v>
       </c>
-      <c r="G12" cm="1">
-        <f t="array" ref="G12">_xlfn.IFS(ISBLANK(A12), "",B12="Sugar Cane", VLOOKUP(C12, $U$48:$V$50, 2, FALSE),_xlfn.IFNA(MATCH(B12, $T$43:$T$47, 0), FALSE), VLOOKUP(B12, $T$43:$V$47, 3, FALSE), TRUE, VLOOKUP(C12, $U$51:$V$53, 2, FALSE))</f>
+      <c r="F12" cm="1">
+        <f t="array" ref="F12">_xlfn.IFS(ISBLANK(A12), "",B12="Sugar Cane", VLOOKUP(C12, $T$48:$U$50, 2, FALSE),_xlfn.IFNA(MATCH(B12, $S$43:$S$47, 0), FALSE), VLOOKUP(B12, $S$43:$U$47, 3, FALSE), TRUE, VLOOKUP(C12, $T$51:$U$53, 2, FALSE))</f>
         <v>0</v>
       </c>
+      <c r="G12" s="14">
+        <v>1700</v>
+      </c>
       <c r="H12" s="14">
-        <f t="shared" si="7"/>
-        <v>100000</v>
-      </c>
-      <c r="I12" s="14">
         <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
-      <c r="J12" s="14">
+      <c r="I12" s="14">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="K12" s="14">
+      <c r="J12" s="14">
         <f t="shared" si="2"/>
         <v>0.88</v>
       </c>
-      <c r="L12" s="14">
+      <c r="K12" s="14">
         <f t="shared" si="3"/>
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="M12" s="14">
+      <c r="L12" s="14">
         <f t="shared" si="8"/>
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="N12" s="14" t="str">
+      <c r="M12" s="14" t="str">
+        <f t="shared" si="4"/>
+        <v>n/a</v>
+      </c>
+      <c r="N12">
         <f t="shared" si="9"/>
-        <v>n/a</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>9.4247999999999994</v>
       </c>
       <c r="P12">
-        <f t="shared" si="4"/>
-        <v>554.4</v>
+        <f t="shared" si="6"/>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="5"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="R12">
-        <f t="shared" si="6"/>
-        <v>5.2271999999999996E-3</v>
-      </c>
-      <c r="T12" s="2" t="s">
+        <f t="shared" si="7"/>
+        <v>8.8862399999999991E-5</v>
+      </c>
+      <c r="S12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="U12" s="2"/>
-    </row>
-    <row r="13" spans="1:22">
+      <c r="T12" s="2"/>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D13">
-        <v>50</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-      <c r="F13">
         <v>0.3</v>
       </c>
-      <c r="G13" cm="1">
-        <f t="array" ref="G13">_xlfn.IFS(ISBLANK(A13), "",B13="Sugar Cane", VLOOKUP(C13, $U$48:$V$50, 2, FALSE),_xlfn.IFNA(MATCH(B13, $T$43:$T$47, 0), FALSE), VLOOKUP(B13, $T$43:$V$47, 3, FALSE), TRUE, VLOOKUP(C13, $U$51:$V$53, 2, FALSE))</f>
+      <c r="F13" cm="1">
+        <f t="array" ref="F13">_xlfn.IFS(ISBLANK(A13), "",B13="Sugar Cane", VLOOKUP(C13, $T$48:$U$50, 2, FALSE),_xlfn.IFNA(MATCH(B13, $S$43:$S$47, 0), FALSE), VLOOKUP(B13, $S$43:$U$47, 3, FALSE), TRUE, VLOOKUP(C13, $T$51:$U$53, 2, FALSE))</f>
         <v>0.8</v>
       </c>
+      <c r="G13" s="14">
+        <v>1800</v>
+      </c>
       <c r="H13" s="14">
-        <f t="shared" si="7"/>
-        <v>100000</v>
-      </c>
-      <c r="I13" s="14">
         <f t="shared" si="0"/>
         <v>1.34</v>
       </c>
-      <c r="J13" s="14">
+      <c r="I13" s="14">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="K13" s="14">
+      <c r="J13" s="14">
         <f t="shared" si="2"/>
         <v>0.88</v>
       </c>
-      <c r="L13" s="14">
+      <c r="K13" s="14">
         <f t="shared" si="3"/>
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="M13" s="14">
+      <c r="L13" s="14">
         <f t="shared" si="8"/>
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="N13" s="14">
+      <c r="M13" s="14">
+        <f t="shared" si="4"/>
+        <v>0.01</v>
+      </c>
+      <c r="N13">
         <f t="shared" si="9"/>
         <v>0.01</v>
       </c>
       <c r="O13">
-        <f t="shared" si="10"/>
-        <v>0.01</v>
+        <f t="shared" si="5"/>
+        <v>6.5799359999999982</v>
       </c>
       <c r="P13">
-        <f t="shared" si="4"/>
-        <v>365.55199999999996</v>
+        <f t="shared" si="6"/>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="5"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="R13">
-        <f t="shared" si="6"/>
-        <v>3.4466331428571425E-3</v>
-      </c>
-      <c r="T13" t="s">
+        <f t="shared" si="7"/>
+        <v>6.2039396571428548E-5</v>
+      </c>
+      <c r="S13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:21">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D14">
-        <v>50</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
-      <c r="F14">
         <v>0.3</v>
       </c>
-      <c r="G14" cm="1">
-        <f t="array" ref="G14">_xlfn.IFS(ISBLANK(A14), "",B14="Sugar Cane", VLOOKUP(C14, $U$48:$V$50, 2, FALSE),_xlfn.IFNA(MATCH(B14, $T$43:$T$47, 0), FALSE), VLOOKUP(B14, $T$43:$V$47, 3, FALSE), TRUE, VLOOKUP(C14, $U$51:$V$53, 2, FALSE))</f>
+      <c r="F14" cm="1">
+        <f t="array" ref="F14">_xlfn.IFS(ISBLANK(A14), "",B14="Sugar Cane", VLOOKUP(C14, $T$48:$U$50, 2, FALSE),_xlfn.IFNA(MATCH(B14, $S$43:$S$47, 0), FALSE), VLOOKUP(B14, $S$43:$U$47, 3, FALSE), TRUE, VLOOKUP(C14, $T$51:$U$53, 2, FALSE))</f>
         <v>7.0000000000000007E-2</v>
       </c>
+      <c r="G14" s="14">
+        <v>1900</v>
+      </c>
       <c r="H14" s="14">
-        <f t="shared" si="7"/>
-        <v>100000</v>
-      </c>
-      <c r="I14" s="14">
         <f t="shared" si="0"/>
         <v>1.37</v>
       </c>
-      <c r="J14" s="14">
+      <c r="I14" s="14">
         <f t="shared" si="1"/>
         <v>0.51</v>
       </c>
-      <c r="K14" s="14">
+      <c r="J14" s="14">
         <f t="shared" si="2"/>
         <v>0.87</v>
       </c>
-      <c r="L14" s="14">
+      <c r="K14" s="14">
         <f t="shared" si="3"/>
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="M14" s="14">
+      <c r="L14" s="14">
         <f t="shared" si="8"/>
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="N14" s="14">
+      <c r="M14" s="14">
+        <f t="shared" si="4"/>
+        <v>0.01</v>
+      </c>
+      <c r="N14">
         <f t="shared" si="9"/>
         <v>0.01</v>
       </c>
       <c r="O14">
-        <f t="shared" si="10"/>
-        <v>0.01</v>
+        <f t="shared" si="5"/>
+        <v>24.389849699999999</v>
       </c>
       <c r="P14">
-        <f t="shared" si="4"/>
-        <v>1283.6762999999999</v>
+        <f t="shared" si="6"/>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
+        <v>2.299614400285714E-4</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="T14" s="2">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="R14">
-        <f t="shared" si="6"/>
-        <v>1.2103233685714285E-2</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="U14" s="2">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="V14" s="9" t="s">
+      <c r="U14" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:21">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="13"/>
-      <c r="H15" s="14" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
       <c r="I15" s="14"/>
       <c r="J15" s="14"/>
       <c r="K15" s="14"/>
       <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14" t="str">
-        <f t="shared" si="9"/>
+      <c r="M15" s="14" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T15" s="2" t="s">
+      <c r="S15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="U15" s="2">
+      <c r="T15" s="2">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="V15" s="9" t="s">
+      <c r="U15" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:21">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="13"/>
-      <c r="G16" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H16" s="14" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+      <c r="F16" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
       <c r="I16" s="14"/>
       <c r="J16" s="14"/>
       <c r="K16" s="14"/>
       <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14" t="str">
-        <f t="shared" si="9"/>
+      <c r="M16" s="14" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
+      <c r="S16" s="2"/>
       <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
-      <c r="V16" s="9"/>
-    </row>
-    <row r="17" spans="1:28">
+      <c r="U16" s="9"/>
+    </row>
+    <row r="17" spans="1:27">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -1902,1043 +1826,1031 @@
         <v>31</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D17">
-        <v>50</v>
+        <v>0.3</v>
       </c>
       <c r="E17">
-        <v>2</v>
-      </c>
-      <c r="F17">
-        <v>0.3</v>
-      </c>
-      <c r="G17" s="5">
-        <v>0.1</v>
+        <v>300</v>
+      </c>
+      <c r="F17" s="5">
+        <f>E17/(G17*H17)</f>
+        <v>0.1040943789035392</v>
+      </c>
+      <c r="G17" s="14">
+        <v>2200</v>
       </c>
       <c r="H17" s="14">
-        <f t="shared" si="7"/>
-        <v>100000</v>
+        <f>IF(ISBLANK($A17), "", VLOOKUP($B17, $S$22:$AA$39, 2, FALSE))</f>
+        <v>1.31</v>
       </c>
       <c r="I17" s="14">
-        <f>IF(ISBLANK($A17), "", VLOOKUP($B17, $T$22:$AB$39, 2, FALSE))</f>
-        <v>1.31</v>
+        <f>IF(ISBLANK($A17), "", VLOOKUP($B17, $S$22:$AA$39, 3, FALSE))</f>
+        <v>0.16</v>
       </c>
       <c r="J17" s="14">
-        <f>IF(ISBLANK($A17), "", VLOOKUP($B17, $T$22:$AB$39, 3, FALSE))</f>
-        <v>0.16</v>
+        <f>IF(ISBLANK($A17), "", VLOOKUP($B17, $S$22:$AA$39, 4, FALSE))</f>
+        <v>0.8</v>
       </c>
       <c r="K17" s="14">
-        <f>IF(ISBLANK($A17), "", VLOOKUP($B17, $T$22:$AB$39, 4, FALSE))</f>
-        <v>0.8</v>
+        <f>IF(ISBLANK($A17), "", VLOOKUP($B17, $S$22:$AA$39, 6, FALSE))</f>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="L17" s="14">
-        <f>IF(ISBLANK($A17), "", VLOOKUP($B17, $T$22:$AB$39, 6, FALSE))</f>
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="M17" s="14">
         <f t="shared" si="8"/>
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="N17" s="14">
+      <c r="M17" s="14">
+        <f t="shared" si="4"/>
+        <v>0.01</v>
+      </c>
+      <c r="N17">
         <f t="shared" si="9"/>
         <v>0.01</v>
       </c>
       <c r="O17">
-        <f t="shared" si="10"/>
-        <v>0.01</v>
+        <f>IF(ISBLANK(A17),"", (G17*H17*(1 - D17 - F17) * J17*L17)+(G17*H17*I17*J17*N17))</f>
+        <v>13.3064</v>
       </c>
       <c r="P17">
-        <f>IF(ISBLANK(A17),"", (H17*I17*(1 - F17 - G17) * K17*M17)+(H17*I17*J17*K17*O17))</f>
-        <v>607.84</v>
+        <f>IF(ISBLANK(A17),"",VLOOKUP(A17,$S$14:$T$30,2,FALSE))</f>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="Q17">
-        <f>IF(ISBLANK(A17),"",VLOOKUP(A17,$T$14:$U$30,2,FALSE))</f>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="R17">
-        <f>IF(ISBLANK(A17), "", P17*Q17*$U$10/1000)</f>
-        <v>5.731062857142857E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:28">
+        <f>IF(ISBLANK(A17), "", O17*P17*$T$10/1000)</f>
+        <v>1.2546034285714286E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27">
       <c r="A18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D18">
-        <v>50</v>
+        <v>0.3</v>
       </c>
       <c r="E18">
-        <v>2</v>
-      </c>
-      <c r="F18">
-        <v>0.3</v>
-      </c>
-      <c r="G18" s="5">
-        <v>0.2</v>
+        <v>350</v>
+      </c>
+      <c r="F18" s="5">
+        <f t="shared" ref="F18:F20" si="10">E18/(G18*H18)</f>
+        <v>0.11107584893684543</v>
+      </c>
+      <c r="G18" s="14">
+        <v>2300</v>
       </c>
       <c r="H18" s="14">
-        <f t="shared" si="7"/>
-        <v>100000</v>
+        <f>IF(ISBLANK($A18), "", VLOOKUP($B18, $S$22:$AA$39, 2, FALSE))</f>
+        <v>1.37</v>
       </c>
       <c r="I18" s="14">
-        <f>IF(ISBLANK($A18), "", VLOOKUP($B18, $T$22:$AB$39, 2, FALSE))</f>
-        <v>1.37</v>
+        <f>IF(ISBLANK($A18), "", VLOOKUP($B18, $S$22:$AA$39, 3, FALSE))</f>
+        <v>0.51</v>
       </c>
       <c r="J18" s="14">
-        <f>IF(ISBLANK($A18), "", VLOOKUP($B18, $T$22:$AB$39, 3, FALSE))</f>
-        <v>0.51</v>
+        <f>IF(ISBLANK($A18), "", VLOOKUP($B18, $S$22:$AA$39, 4, FALSE))</f>
+        <v>0.87</v>
       </c>
       <c r="K18" s="14">
-        <f>IF(ISBLANK($A18), "", VLOOKUP($B18, $T$22:$AB$39, 4, FALSE))</f>
-        <v>0.87</v>
+        <f>IF(ISBLANK($A18), "", VLOOKUP($B18, $S$22:$AA$39, 6, FALSE))</f>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="L18" s="14">
-        <f>IF(ISBLANK($A18), "", VLOOKUP($B18, $T$22:$AB$39, 6, FALSE))</f>
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="M18" s="14">
         <f t="shared" si="8"/>
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="N18" s="14">
+      <c r="M18" s="14">
+        <f t="shared" si="4"/>
+        <v>0.01</v>
+      </c>
+      <c r="N18">
         <f t="shared" si="9"/>
         <v>0.01</v>
       </c>
       <c r="O18">
-        <f t="shared" si="10"/>
-        <v>0.01</v>
+        <f>IF(ISBLANK(A18),"", (G18*H18*(1 - D18 - F18) * J18*L18)+(G18*H18*I18*J18*N18))</f>
+        <v>28.511118000000003</v>
       </c>
       <c r="P18">
-        <f>IF(ISBLANK(A18),"", (H18*I18*(1 - F18 - G18) * K18*M18)+(H18*I18*J18*K18*O18))</f>
-        <v>1144.2239999999997</v>
+        <f>IF(ISBLANK(A18),"",VLOOKUP(A18,$S$14:$T$30,2,FALSE))</f>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="Q18">
-        <f>IF(ISBLANK(A18),"",VLOOKUP(A18,$T$14:$U$30,2,FALSE))</f>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="R18">
-        <f>IF(ISBLANK(A18), "", P18*Q18*$U$10/1000)</f>
-        <v>1.0788397714285712E-2</v>
-      </c>
+        <f>IF(ISBLANK(A18), "", O18*P18*$T$10/1000)</f>
+        <v>2.6881911257142858E-4</v>
+      </c>
+      <c r="S18" s="2"/>
       <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
-    </row>
-    <row r="19" spans="1:28">
+    </row>
+    <row r="19" spans="1:27">
       <c r="A19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D19">
-        <v>50</v>
+        <v>0.3</v>
       </c>
       <c r="E19">
-        <v>2</v>
-      </c>
-      <c r="F19">
-        <v>0.3</v>
-      </c>
-      <c r="G19" s="5">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="F19" s="5">
+        <f t="shared" si="10"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="G19" s="14">
+        <v>2400</v>
       </c>
       <c r="H19" s="14">
-        <f t="shared" si="7"/>
-        <v>100000</v>
+        <f>IF(ISBLANK($A19), "", VLOOKUP($B19, $S$22:$AA$39, 2, FALSE))</f>
+        <v>1.5</v>
       </c>
       <c r="I19" s="14">
-        <f>IF(ISBLANK($A19), "", VLOOKUP($B19, $T$22:$AB$39, 2, FALSE))</f>
-        <v>1.5</v>
+        <f>IF(ISBLANK($A19), "", VLOOKUP($B19, $S$22:$AA$39, 3, FALSE))</f>
+        <v>0.28999999999999998</v>
       </c>
       <c r="J19" s="14">
-        <f>IF(ISBLANK($A19), "", VLOOKUP($B19, $T$22:$AB$39, 3, FALSE))</f>
-        <v>0.28999999999999998</v>
+        <f>IF(ISBLANK($A19), "", VLOOKUP($B19, $S$22:$AA$39, 4, FALSE))</f>
+        <v>0.88</v>
       </c>
       <c r="K19" s="14">
-        <f>IF(ISBLANK($A19), "", VLOOKUP($B19, $T$22:$AB$39, 4, FALSE))</f>
-        <v>0.88</v>
+        <f>IF(ISBLANK($A19), "", VLOOKUP($B19, $S$22:$AA$39, 6, FALSE))</f>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="L19" s="14">
-        <f>IF(ISBLANK($A19), "", VLOOKUP($B19, $T$22:$AB$39, 6, FALSE))</f>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="M19" s="14">
         <f t="shared" si="8"/>
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="N19" s="14" t="str">
+      <c r="M19" s="14" t="str">
+        <f t="shared" si="4"/>
+        <v>n/a</v>
+      </c>
+      <c r="N19">
         <f t="shared" si="9"/>
-        <v>n/a</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f>IF(ISBLANK(A19),"", (G19*H19*(1 - D19 - F19) * J19*L19)+(G19*H19*I19*J19*N19))</f>
+        <v>11.193599999999998</v>
       </c>
       <c r="P19">
-        <f>IF(ISBLANK(A19),"", (H19*I19*(1 - F19 - G19) * K19*M19)+(H19*I19*J19*K19*O19))</f>
-        <v>554.4</v>
+        <f>IF(ISBLANK(A19),"",VLOOKUP(A19,$S$14:$T$30,2,FALSE))</f>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="Q19">
-        <f>IF(ISBLANK(A19),"",VLOOKUP(A19,$T$14:$U$30,2,FALSE))</f>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="R19">
-        <f>IF(ISBLANK(A19), "", P19*Q19*$U$10/1000)</f>
-        <v>5.2271999999999996E-3</v>
-      </c>
+        <f>IF(ISBLANK(A19), "", O19*P19*$T$10/1000)</f>
+        <v>1.0553965714285712E-4</v>
+      </c>
+      <c r="S19" s="2"/>
       <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-    </row>
-    <row r="20" spans="1:28">
+    </row>
+    <row r="20" spans="1:27">
       <c r="A20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>34</v>
       </c>
       <c r="D20">
-        <v>50</v>
+        <v>0.3</v>
       </c>
       <c r="E20">
-        <v>2</v>
-      </c>
-      <c r="F20">
-        <v>0.3</v>
-      </c>
-      <c r="G20" s="5">
+        <v>5</v>
+      </c>
+      <c r="F20" s="5">
+        <f t="shared" si="10"/>
+        <v>2E-3</v>
+      </c>
+      <c r="G20" s="14">
+        <v>2500</v>
+      </c>
+      <c r="H20" s="14">
+        <f>IF(ISBLANK($A20), "", VLOOKUP($B20, $S$22:$AA$39, 2, FALSE))</f>
         <v>1</v>
       </c>
-      <c r="H20" s="14">
-        <f t="shared" si="7"/>
-        <v>100000</v>
-      </c>
       <c r="I20" s="14">
-        <f>IF(ISBLANK($A20), "", VLOOKUP($B20, $T$22:$AB$39, 2, FALSE))</f>
-        <v>1</v>
+        <f>IF(ISBLANK($A20), "", VLOOKUP($B20, $S$22:$AA$39, 3, FALSE))</f>
+        <v>0.22</v>
       </c>
       <c r="J20" s="14">
-        <f>IF(ISBLANK($A20), "", VLOOKUP($B20, $T$22:$AB$39, 3, FALSE))</f>
-        <v>0.22</v>
+        <f>IF(ISBLANK($A20), "", VLOOKUP($B20, $S$22:$AA$39, 4, FALSE))</f>
+        <v>0.85</v>
       </c>
       <c r="K20" s="14">
-        <f>IF(ISBLANK($A20), "", VLOOKUP($B20, $T$22:$AB$39, 4, FALSE))</f>
-        <v>0.85</v>
+        <f>IF(ISBLANK($A20), "", VLOOKUP($B20, $S$22:$AA$39, 6, FALSE))</f>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="L20" s="14">
-        <f>IF(ISBLANK($A20), "", VLOOKUP($B20, $T$22:$AB$39, 6, FALSE))</f>
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="M20" s="14">
         <f t="shared" si="8"/>
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="N20" s="14">
+      <c r="M20" s="14">
+        <f t="shared" si="4"/>
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="N20">
         <f t="shared" si="9"/>
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="O20">
-        <f t="shared" si="10"/>
-        <v>8.9999999999999993E-3</v>
+        <f>IF(ISBLANK(A20),"", (G20*H20*(1 - D20 - F20) * J20*L20)+(G20*H20*I20*J20*N20))</f>
+        <v>16.073499999999996</v>
       </c>
       <c r="P20">
-        <f>IF(ISBLANK(A20),"", (H20*I20*(1 - F20 - G20) * K20*M20)+(H20*I20*J20*K20*O20))</f>
-        <v>-35.700000000000045</v>
+        <f>IF(ISBLANK(A20),"",VLOOKUP(A20,$S$14:$T$30,2,FALSE))</f>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="Q20">
-        <f>IF(ISBLANK(A20),"",VLOOKUP(A20,$T$14:$U$30,2,FALSE))</f>
+        <f>IF(ISBLANK(A20), "", O20*P20*$T$10/1000)</f>
+        <v>1.5155014285714281E-4</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T20" s="2"/>
+    </row>
+    <row r="21" spans="1:27" ht="17">
+      <c r="S21" s="2"/>
+      <c r="T21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U21" t="s">
+        <v>18</v>
+      </c>
+      <c r="V21" t="s">
+        <v>19</v>
+      </c>
+      <c r="W21" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="X21" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27">
+      <c r="S22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T22" s="12">
+        <v>1.5</v>
+      </c>
+      <c r="U22" s="11">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="V22" s="11">
+        <v>0.88</v>
+      </c>
+      <c r="W22" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="X22" s="11">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="R20">
-        <f>IF(ISBLANK(A20), "", P20*Q20*$U$10/1000)</f>
-        <v>-3.3660000000000043E-4</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="U20" s="2"/>
-    </row>
-    <row r="21" spans="1:28" ht="17">
-      <c r="T21" s="2"/>
-      <c r="U21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="V21" t="s">
-        <v>18</v>
-      </c>
-      <c r="W21" t="s">
-        <v>19</v>
-      </c>
-      <c r="X21" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:28">
-      <c r="T22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="U22" s="12">
-        <v>1.5</v>
-      </c>
-      <c r="V22" s="11">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="W22" s="11">
-        <v>0.88</v>
-      </c>
-      <c r="X22" s="11">
-        <v>0.4</v>
-      </c>
       <c r="Y22" s="11">
-        <v>6.0000000000000001E-3</v>
+        <v>0.01</v>
       </c>
       <c r="Z22" s="11">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
       <c r="AA22" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="AB22" s="11">
         <v>0.9</v>
       </c>
     </row>
-    <row r="23" spans="1:28">
+    <row r="23" spans="1:27">
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
-      <c r="N23" s="14"/>
-      <c r="T23" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="U23" s="12">
+      <c r="M23" s="14"/>
+      <c r="S23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T23" s="12">
         <v>1.24</v>
       </c>
+      <c r="U23" s="11">
+        <v>0.32</v>
+      </c>
       <c r="V23" s="11">
-        <v>0.32</v>
+        <v>0.88</v>
       </c>
       <c r="W23" s="11">
-        <v>0.88</v>
+        <v>0.4</v>
       </c>
       <c r="X23" s="11">
-        <v>0.4</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="Y23" s="11">
-        <v>7.0000000000000001E-3</v>
+        <v>0.01</v>
       </c>
       <c r="Z23" s="11">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
       <c r="AA23" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="AB23" s="11">
         <v>0.85</v>
       </c>
     </row>
-    <row r="24" spans="1:28">
+    <row r="24" spans="1:27">
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
-      <c r="T24" s="2" t="s">
+      <c r="S24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="T24" s="12">
+        <v>0.81</v>
+      </c>
+      <c r="U24" s="11">
+        <v>0.39</v>
+      </c>
+      <c r="V24" s="11">
+        <v>0.85</v>
+      </c>
+      <c r="W24" s="11">
+        <v>0.42</v>
+      </c>
+      <c r="X24" s="11">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="Y24" s="11">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="Z24" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="11">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27">
+      <c r="O25" t="e">
+        <f>IF(ISBLANK(#REF!), "", H25/#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="S25" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="U24" s="12">
-        <v>0.81</v>
-      </c>
-      <c r="V24" s="11">
-        <v>0.39</v>
-      </c>
-      <c r="W24" s="11">
+      <c r="T25" s="12">
+        <v>1.42</v>
+      </c>
+      <c r="U25" s="11">
+        <v>0.43</v>
+      </c>
+      <c r="V25" s="11">
+        <v>0.88</v>
+      </c>
+      <c r="W25" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="X25" s="11">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="Y25" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="Z25" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="AA25" s="11">
         <v>0.85</v>
       </c>
-      <c r="X24" s="11">
+    </row>
+    <row r="26" spans="1:27">
+      <c r="O26" t="e">
+        <f>IF(ISBLANK(#REF!), "", H26/#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T26" s="12">
+        <v>1.31</v>
+      </c>
+      <c r="U26" s="11">
+        <v>0.16</v>
+      </c>
+      <c r="V26" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="W26" s="11">
         <v>0.42</v>
       </c>
-      <c r="Y24" s="11">
+      <c r="X26" s="11">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="Y26" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="Z26" s="11">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="11">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27">
+      <c r="O27" t="e">
+        <f>IF(ISBLANK(#REF!), "", H27/#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="T27" s="12">
+        <v>1.5</v>
+      </c>
+      <c r="U27" s="11">
+        <v>0.22</v>
+      </c>
+      <c r="V27" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="W27" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="X27" s="11">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="Y27" s="11">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="Z27" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="AA27" s="11">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27">
+      <c r="O28" t="e">
+        <f>IF(ISBLANK(#REF!), "", H28/#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T28" s="12">
+        <v>1.5</v>
+      </c>
+      <c r="U28" s="11">
+        <v>0.42</v>
+      </c>
+      <c r="V28" s="11">
+        <v>0.88</v>
+      </c>
+      <c r="W28" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="X28" s="11">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="Y28" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="Z28" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="AA28" s="11">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27">
+      <c r="S29" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="T29" s="12">
+        <v>1.46</v>
+      </c>
+      <c r="U29" s="11">
+        <v>0.36</v>
+      </c>
+      <c r="V29" s="11">
+        <v>0.88</v>
+      </c>
+      <c r="W29" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="X29" s="11">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="Y29" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="Z29" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="AA29" s="11">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27">
+      <c r="S30" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="T30" s="12">
+        <v>1.37</v>
+      </c>
+      <c r="U30" s="11">
+        <v>0.51</v>
+      </c>
+      <c r="V30" s="11">
+        <v>0.87</v>
+      </c>
+      <c r="W30" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="X30" s="11">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="Y30" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="Z30" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="AA30" s="11">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27">
+      <c r="S31" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T31" s="12">
+        <v>0.34</v>
+      </c>
+      <c r="U31" s="11">
+        <v>0.43</v>
+      </c>
+      <c r="V31" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="W31" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="X31" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="Y31" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="Z31" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA31" s="11">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27">
+      <c r="S32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T32" s="12">
+        <v>1.07</v>
+      </c>
+      <c r="U32" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="V32" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="W32" s="11">
+        <v>0.42</v>
+      </c>
+      <c r="X32" s="11">
+        <v>1.6E-2</v>
+      </c>
+      <c r="Y32" s="11">
+        <v>1.4E-2</v>
+      </c>
+      <c r="Z32" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="AA32" s="11">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="33" spans="19:27">
+      <c r="S33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T33" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="U33" s="11">
+        <v>0.45</v>
+      </c>
+      <c r="V33" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="W33" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="X33" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="Z24" s="11">
+      <c r="Y33" s="11">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="AA24" s="11">
+      <c r="Z33" s="11">
         <v>1</v>
       </c>
-      <c r="AB24" s="11">
+      <c r="AA33" s="11">
         <v>0.8</v>
       </c>
     </row>
-    <row r="25" spans="1:28">
-      <c r="P25" t="str">
-        <f>IF(ISBLANK(D25), "", I25/D25)</f>
-        <v/>
-      </c>
-      <c r="T25" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="U25" s="12">
-        <v>1.42</v>
-      </c>
-      <c r="V25" s="11">
-        <v>0.43</v>
-      </c>
-      <c r="W25" s="11">
+    <row r="34" spans="19:27">
+      <c r="S34" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T34" s="12">
+        <v>1.9</v>
+      </c>
+      <c r="U34" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="V34" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="W34" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="X34" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="Y34" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="Z34" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA34" s="11">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="35" spans="19:27">
+      <c r="S35" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T35" s="12">
+        <v>1.5</v>
+      </c>
+      <c r="U35" s="11">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="V35" s="11">
         <v>0.88</v>
       </c>
-      <c r="X25" s="11">
+      <c r="W35" s="11">
         <v>0.4</v>
       </c>
-      <c r="Y25" s="11">
+      <c r="X35" s="11">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="Z25" s="11">
-        <v>0.01</v>
-      </c>
-      <c r="AA25" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="AB25" s="11">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:28">
-      <c r="P26" t="str">
-        <f>IF(ISBLANK(D26), "", I26/D26)</f>
-        <v/>
-      </c>
-      <c r="T26" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="U26" s="12">
-        <v>1.31</v>
-      </c>
-      <c r="V26" s="11">
-        <v>0.16</v>
-      </c>
-      <c r="W26" s="11">
-        <v>0.8</v>
-      </c>
-      <c r="X26" s="11">
-        <v>0.42</v>
-      </c>
-      <c r="Y26" s="11">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="Z26" s="11">
-        <v>0.01</v>
-      </c>
-      <c r="AA26" s="11">
-        <v>1</v>
-      </c>
-      <c r="AB26" s="11">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:28">
-      <c r="P27" t="str">
-        <f>IF(ISBLANK(D27), "", I27/D27)</f>
-        <v/>
-      </c>
-      <c r="T27" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U27" s="12">
-        <v>1.5</v>
-      </c>
-      <c r="V27" s="11">
-        <v>0.22</v>
-      </c>
-      <c r="W27" s="11">
-        <v>0.8</v>
-      </c>
-      <c r="X27" s="11">
-        <v>0.4</v>
-      </c>
-      <c r="Y27" s="11">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="Z27" s="11">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="AA27" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="AB27" s="11">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:28">
-      <c r="P28" t="str">
-        <f>IF(ISBLANK(D28), "", I28/D28)</f>
-        <v/>
-      </c>
-      <c r="T28" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="U28" s="12">
-        <v>1.5</v>
-      </c>
-      <c r="V28" s="11">
-        <v>0.42</v>
-      </c>
-      <c r="W28" s="11">
-        <v>0.88</v>
-      </c>
-      <c r="X28" s="11">
-        <v>0.4</v>
-      </c>
-      <c r="Y28" s="11">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="Z28" s="11">
-        <v>0.01</v>
-      </c>
-      <c r="AA28" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="AB28" s="11">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="29" spans="1:28">
-      <c r="T29" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="U29" s="12">
-        <v>1.46</v>
-      </c>
-      <c r="V29" s="11">
-        <v>0.36</v>
-      </c>
-      <c r="W29" s="11">
-        <v>0.88</v>
-      </c>
-      <c r="X29" s="11">
-        <v>0.4</v>
-      </c>
-      <c r="Y29" s="11">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="Z29" s="11">
-        <v>0.01</v>
-      </c>
-      <c r="AA29" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="AB29" s="11">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:28">
-      <c r="T30" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="U30" s="12">
-        <v>1.37</v>
-      </c>
-      <c r="V30" s="11">
-        <v>0.51</v>
-      </c>
-      <c r="W30" s="11">
-        <v>0.87</v>
-      </c>
-      <c r="X30" s="11">
-        <v>0.4</v>
-      </c>
-      <c r="Y30" s="11">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="Z30" s="11">
-        <v>0.01</v>
-      </c>
-      <c r="AA30" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="AB30" s="11">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="31" spans="1:28">
-      <c r="T31" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U31" s="12">
-        <v>0.34</v>
-      </c>
-      <c r="V31" s="11">
-        <v>0.43</v>
-      </c>
-      <c r="W31" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="X31" s="11">
-        <v>0.4</v>
-      </c>
-      <c r="Y31" s="11">
-        <v>0.02</v>
-      </c>
-      <c r="Z31" s="11">
-        <v>0.01</v>
-      </c>
-      <c r="AA31" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="AB31" s="11">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="32" spans="1:28">
-      <c r="T32" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="U32" s="12">
-        <v>1.07</v>
-      </c>
-      <c r="V32" s="11">
-        <v>0.2</v>
-      </c>
-      <c r="W32" s="11">
-        <v>0.8</v>
-      </c>
-      <c r="X32" s="11">
-        <v>0.42</v>
-      </c>
-      <c r="Y32" s="11">
-        <v>1.6E-2</v>
-      </c>
-      <c r="Z32" s="11">
-        <v>1.4E-2</v>
-      </c>
-      <c r="AA32" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="AB32" s="11">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="33" spans="20:28">
-      <c r="T33" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U33" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="V33" s="11">
-        <v>0.45</v>
-      </c>
-      <c r="W33" s="11">
-        <v>0.2</v>
-      </c>
-      <c r="X33" s="11">
-        <v>0.4</v>
-      </c>
-      <c r="Y33" s="11">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="Z33" s="11">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="AA33" s="11">
-        <v>1</v>
-      </c>
-      <c r="AB33" s="11">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="34" spans="20:28">
-      <c r="T34" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="U34" s="12">
-        <v>1.9</v>
-      </c>
-      <c r="V34" s="11">
-        <v>0.3</v>
-      </c>
-      <c r="W34" s="11">
-        <v>0.9</v>
-      </c>
-      <c r="X34" s="11">
-        <v>0.4</v>
-      </c>
-      <c r="Y34" s="11">
-        <v>0.01</v>
-      </c>
-      <c r="Z34" s="11">
-        <v>0.01</v>
-      </c>
-      <c r="AA34" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="AB34" s="11">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="35" spans="20:28">
-      <c r="T35" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="U35" s="12">
-        <v>1.5</v>
-      </c>
-      <c r="V35" s="11">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="W35" s="11">
-        <v>0.88</v>
-      </c>
-      <c r="X35" s="11">
-        <v>0.4</v>
-      </c>
-      <c r="Y35" s="11">
-        <v>6.0000000000000001E-3</v>
+      <c r="Y35" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="Z35" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="AA35" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="AB35" s="11">
+      <c r="AA35" s="11">
         <v>0.85</v>
       </c>
     </row>
-    <row r="36" spans="20:28">
-      <c r="T36" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="U36" s="12">
+    <row r="36" spans="19:27">
+      <c r="S36" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="T36" s="12">
         <v>2.08</v>
       </c>
+      <c r="U36" s="11">
+        <v>0.33</v>
+      </c>
       <c r="V36" s="11">
-        <v>0.33</v>
+        <v>0.96</v>
       </c>
       <c r="W36" s="11">
-        <v>0.96</v>
+        <v>0.4</v>
       </c>
       <c r="X36" s="11">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="Y36" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="Z36" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="AA36" s="11">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="37" spans="19:27">
+      <c r="S37" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T37" s="12">
+        <v>1.34</v>
+      </c>
+      <c r="U37" s="11">
+        <v>0.37</v>
+      </c>
+      <c r="V37" s="11">
+        <v>0.88</v>
+      </c>
+      <c r="W37" s="11">
         <v>0.4</v>
       </c>
-      <c r="Y36" s="11">
+      <c r="X37" s="11">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="Y37" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="Z37" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA37" s="11">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="38" spans="19:27">
+      <c r="S38" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="T38" s="10">
+        <v>1</v>
+      </c>
+      <c r="U38" s="10">
+        <v>0.22</v>
+      </c>
+      <c r="V38" s="10">
+        <v>0.85</v>
+      </c>
+      <c r="W38" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="X38" s="10">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="Y38" s="10">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="Z36" s="11">
-        <v>0.01</v>
-      </c>
-      <c r="AA36" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="AB36" s="11">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="37" spans="20:28">
-      <c r="T37" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U37" s="12">
-        <v>1.34</v>
-      </c>
-      <c r="V37" s="11">
-        <v>0.37</v>
-      </c>
-      <c r="W37" s="11">
+      <c r="Z38" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA38" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="19:27">
+      <c r="S39" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="T39" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="U39" s="10">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="V39" s="10">
         <v>0.88</v>
       </c>
-      <c r="X37" s="11">
+      <c r="W39" s="10">
         <v>0.4</v>
       </c>
-      <c r="Y37" s="11">
+      <c r="X39" s="10">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="Z37" s="11">
-        <v>0.01</v>
-      </c>
-      <c r="AA37" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="AB37" s="11">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="38" spans="20:28">
-      <c r="T38" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="U38" s="10">
-        <v>1</v>
-      </c>
-      <c r="V38" s="10">
-        <v>0.22</v>
-      </c>
-      <c r="W38" s="10">
-        <v>0.85</v>
-      </c>
-      <c r="X38" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="Y38" s="10">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="Z38" s="10">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="AA38" s="10" t="s">
+      <c r="Y39" s="10" t="s">
         <v>16</v>
-      </c>
-      <c r="AB38" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="20:28">
-      <c r="T39" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="U39" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="V39" s="10">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="W39" s="10">
-        <v>0.88</v>
-      </c>
-      <c r="X39" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="Y39" s="10">
-        <v>6.0000000000000001E-3</v>
       </c>
       <c r="Z39" s="10" t="s">
         <v>16</v>
       </c>
       <c r="AA39" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB39" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="40" spans="20:28">
-      <c r="T40" s="2"/>
-      <c r="U40" s="12"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="19:27">
+      <c r="S40" s="2"/>
+      <c r="T40" s="12"/>
+      <c r="U40" s="11"/>
       <c r="V40" s="11"/>
       <c r="W40" s="11"/>
       <c r="X40" s="11"/>
       <c r="Y40" s="11"/>
       <c r="Z40" s="11"/>
       <c r="AA40" s="11"/>
-      <c r="AB40" s="11"/>
-    </row>
-    <row r="41" spans="20:28">
+    </row>
+    <row r="41" spans="19:27">
+      <c r="S41" s="2"/>
       <c r="T41" s="2"/>
-      <c r="U41" s="2"/>
-    </row>
-    <row r="42" spans="20:28">
+    </row>
+    <row r="42" spans="19:27">
+      <c r="S42" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="T42" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="U42" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="V42" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="20:28">
+    <row r="43" spans="19:27">
+      <c r="S43" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="T43" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="U43" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V43">
+      <c r="U43">
         <v>0.06</v>
       </c>
     </row>
-    <row r="44" spans="20:28">
+    <row r="44" spans="19:27">
+      <c r="S44" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="T44" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U44" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V44">
+      <c r="U44">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="20:28">
-      <c r="T45" t="s">
+    <row r="45" spans="19:27">
+      <c r="S45" t="s">
         <v>3</v>
       </c>
-      <c r="U45" s="2" t="s">
+      <c r="T45" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V45">
+      <c r="U45">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="20:28">
+    <row r="46" spans="19:27">
+      <c r="S46" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="T46" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="U46" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V46">
+      <c r="U46">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="20:28">
+    <row r="47" spans="19:27">
+      <c r="S47" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="T47" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U47" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="V47">
+      <c r="U47">
         <v>0.8</v>
       </c>
     </row>
-    <row r="48" spans="20:28">
+    <row r="48" spans="19:27">
+      <c r="S48" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="T48" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="19:21">
+      <c r="S49" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="U48" s="2" t="s">
+      <c r="T49" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U49">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="50" spans="19:21">
+      <c r="S50" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T50" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="19:21">
+      <c r="S51" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T51" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="V48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="20:22">
-      <c r="T49" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="U49" s="2" t="s">
+      <c r="U51">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="52" spans="19:21">
+      <c r="S52" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T52" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="U52">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="19:21">
+      <c r="S53" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T53" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V49">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="50" spans="20:22">
-      <c r="T50" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="U50" s="2" t="s">
+      <c r="U53">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="54" spans="19:21">
+      <c r="S54" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T54" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="U54">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="55" spans="19:21">
+      <c r="S55" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T55" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="V50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="20:22">
-      <c r="T51" s="2" t="s">
+      <c r="U55">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="56" spans="19:21">
+      <c r="S56" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U51" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="V51">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="52" spans="20:22">
-      <c r="T52" s="2" t="s">
+      <c r="T56" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="U56">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="57" spans="19:21">
+      <c r="S57" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U52" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V52">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="20:22">
-      <c r="T53" s="2" t="s">
+      <c r="T57" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="U57">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="58" spans="19:21">
+      <c r="S58" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V53">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="54" spans="20:22">
-      <c r="T54" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="U54" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="V54">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="55" spans="20:22">
-      <c r="T55" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="U55" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V55">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="56" spans="20:22">
-      <c r="T56" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="U56" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="V56">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="57" spans="20:22">
-      <c r="T57" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="U57" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="V57">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="58" spans="20:22">
       <c r="T58" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="U58" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="V58">
+        <v>59</v>
+      </c>
+      <c r="U58">
         <v>0</v>
       </c>
     </row>
@@ -2946,7 +2858,7 @@
   <dataConsolidate/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="N5" formula="1"/>
+    <ignoredError sqref="M5" formula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/packages/calculators/src/modules/test/6.1-crop-residues.xlsx
+++ b/packages/calculators/src/modules/test/6.1-crop-residues.xlsx
@@ -1,20 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2393B0D-E024-114F-AA9D-6F037E3E6E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD05233-11B6-2149-A3FB-BDB7C462538F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15940" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="6.1.1.1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -662,7 +660,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -684,7 +682,6 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf applyFill="1" numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -700,6 +697,28 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="common"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="common_cn2o" refersTo="='common'!$B$4"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="B4">
+            <v>1.57</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1102,7 +1121,7 @@
       <c r="F4" t="s">
         <v>29</v>
       </c>
-      <c r="G4" t="s" s="15">
+      <c r="G4" s="5" t="s">
         <v>41</v>
       </c>
       <c r="H4" t="s">
@@ -1192,7 +1211,7 @@
       </c>
       <c r="Q5">
         <f t="shared" ref="Q5:Q14" si="7">IF(ISBLANK(A5), "", O5*P5*$T$10/1000)</f>
-        <v>3.3707142857142858E-6</v>
+        <v>3.3676500000000003E-6</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -1253,7 +1272,7 @@
       </c>
       <c r="Q6">
         <f t="shared" si="7"/>
-        <v>3.0898214285714286E-6</v>
+        <v>3.0870125000000003E-6</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -1314,7 +1333,7 @@
       </c>
       <c r="Q7">
         <f t="shared" si="7"/>
-        <v>8.039297828571429E-5</v>
+        <v>8.0319893760000011E-5</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -1375,7 +1394,7 @@
       </c>
       <c r="Q8">
         <f t="shared" si="7"/>
-        <v>8.7092393142857149E-5</v>
+        <v>8.7013218240000008E-5</v>
       </c>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
@@ -1438,7 +1457,7 @@
       </c>
       <c r="Q9">
         <f t="shared" si="7"/>
-        <v>3.3660000000000062E-7</v>
+        <v>3.3629400000000059E-7</v>
       </c>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
@@ -1501,14 +1520,14 @@
       </c>
       <c r="Q10">
         <f t="shared" si="7"/>
-        <v>-2.0436428571428582E-6</v>
+        <v>-2.0417850000000012E-6</v>
       </c>
       <c r="S10" t="s">
         <v>2</v>
       </c>
       <c r="T10">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -1569,7 +1588,7 @@
       </c>
       <c r="Q11">
         <f t="shared" si="7"/>
-        <v>2.5796571428571432E-4</v>
+        <v>2.5773119999999999E-4</v>
       </c>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
@@ -1632,7 +1651,7 @@
       </c>
       <c r="Q12">
         <f t="shared" si="7"/>
-        <v>8.8862399999999991E-5</v>
+        <v>8.8781615999999994E-5</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>6</v>
@@ -1697,7 +1716,7 @@
       </c>
       <c r="Q13">
         <f t="shared" si="7"/>
-        <v>6.2039396571428548E-5</v>
+        <v>6.1982997119999989E-5</v>
       </c>
       <c r="S13" t="s">
         <v>7</v>
@@ -1761,7 +1780,7 @@
       </c>
       <c r="Q14">
         <f t="shared" si="7"/>
-        <v>2.299614400285714E-4</v>
+        <v>2.2975238417399999E-4</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>10</v>
@@ -1879,7 +1898,7 @@
       </c>
       <c r="Q17">
         <f>IF(ISBLANK(A17), "", O17*P17*$T$10/1000)</f>
-        <v>1.2546034285714286E-4</v>
+        <v>1.2534628799999999E-4</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -1943,7 +1962,7 @@
       </c>
       <c r="Q18">
         <f>IF(ISBLANK(A18), "", O18*P18*$T$10/1000)</f>
-        <v>2.6881911257142858E-4</v>
+        <v>2.6857473156000002E-4</v>
       </c>
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
@@ -2009,7 +2028,7 @@
       </c>
       <c r="Q19">
         <f>IF(ISBLANK(A19), "", O19*P19*$T$10/1000)</f>
-        <v>1.0553965714285712E-4</v>
+        <v>1.0544371199999999E-4</v>
       </c>
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
@@ -2075,7 +2094,7 @@
       </c>
       <c r="Q20">
         <f>IF(ISBLANK(A20), "", O20*P20*$T$10/1000)</f>
-        <v>1.5155014285714281E-4</v>
+        <v>1.5141236999999995E-4</v>
       </c>
       <c r="S20" s="2" t="s">
         <v>15</v>

--- a/packages/calculators/src/modules/test/6.1-crop-residues.xlsx
+++ b/packages/calculators/src/modules/test/6.1-crop-residues.xlsx
@@ -1202,7 +1202,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="O5">
-        <f t="shared" ref="O5:O14" si="5">IF(ISBLANK(A5),"", (G5*H5*(1 - D5 - F5) * J5*L5)+(G5*H5*I5*J5*N5))</f>
+        <f t="shared" ref="O5:O14" si="5">IF(ISBLANK(A5),"", (G5*H5*(1 - IF(ISNUMBER(VLOOKUP($B5, $S$22:$AA$39, 8, FALSE)), D5, 0) - F5) * J5*L5)+(G5*H5*I5*J5*N5))</f>
         <v>0.35750000000000004</v>
       </c>
       <c r="P5">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="O9">
         <f t="shared" si="5"/>
-        <v>3.5700000000000065E-2</v>
+        <v>0.5117</v>
       </c>
       <c r="P9">
         <f t="shared" si="6"/>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="Q9">
         <f t="shared" si="7"/>
-        <v>3.3629400000000059E-7</v>
+        <v>4.820214000000001e-06</v>
       </c>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="O10">
         <f t="shared" si="5"/>
-        <v>-0.21675000000000011</v>
+        <v>0.54825</v>
       </c>
       <c r="P10">
         <f t="shared" si="6"/>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="Q10">
         <f t="shared" si="7"/>
-        <v>-2.0417850000000012E-6</v>
+        <v>5.1645150000000005e-06</v>
       </c>
       <c r="S10" t="s">
         <v>2</v>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11">
         <f t="shared" si="5"/>
-        <v>27.36</v>
+        <v>35.568</v>
       </c>
       <c r="P11">
         <f t="shared" si="6"/>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="Q11">
         <f t="shared" si="7"/>
-        <v>2.5773119999999999E-4</v>
+        <v>0.00033505055999999997</v>
       </c>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="O12">
         <f t="shared" si="5"/>
-        <v>9.4247999999999994</v>
+        <v>13.464</v>
       </c>
       <c r="P12">
         <f t="shared" si="6"/>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="Q12">
         <f t="shared" si="7"/>
-        <v>8.8781615999999994E-5</v>
+        <v>0.00012683088</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>6</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="O13">
         <f t="shared" si="5"/>
-        <v>6.5799359999999982</v>
+        <v>10.400543999999998</v>
       </c>
       <c r="P13">
         <f t="shared" si="6"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="Q13">
         <f t="shared" si="7"/>
-        <v>6.1982997119999989E-5</v>
+        <v>9.797312447999999e-05</v>
       </c>
       <c r="S13" t="s">
         <v>7</v>
@@ -1889,7 +1889,7 @@
         <v>0.01</v>
       </c>
       <c r="O17">
-        <f>IF(ISBLANK(A17),"", (G17*H17*(1 - D17 - F17) * J17*L17)+(G17*H17*I17*J17*N17))</f>
+        <f>IF(ISBLANK(A17),"", (G17*H17*(1 - IF(ISNUMBER(VLOOKUP($B17, $S$22:$AA$39, 8, FALSE)), D17, 0) - F17) * J17*L17)+(G17*H17*I17*J17*N17))</f>
         <v>13.3064</v>
       </c>
       <c r="P17">
@@ -1953,7 +1953,7 @@
         <v>0.01</v>
       </c>
       <c r="O18">
-        <f>IF(ISBLANK(A18),"", (G18*H18*(1 - D18 - F18) * J18*L18)+(G18*H18*I18*J18*N18))</f>
+        <f>IF(ISBLANK(A18),"", (G18*H18*(1 - IF(ISNUMBER(VLOOKUP($B18, $S$22:$AA$39, 8, FALSE)), D18, 0) - F18) * J18*L18)+(G18*H18*I18*J18*N18))</f>
         <v>28.511118000000003</v>
       </c>
       <c r="P18">
@@ -2019,8 +2019,8 @@
         <v>0</v>
       </c>
       <c r="O19">
-        <f>IF(ISBLANK(A19),"", (G19*H19*(1 - D19 - F19) * J19*L19)+(G19*H19*I19*J19*N19))</f>
-        <v>11.193599999999998</v>
+        <f>IF(ISBLANK(A19),"", (G19*H19*(1 - IF(ISNUMBER(VLOOKUP($B19, $S$22:$AA$39, 8, FALSE)), D19, 0) - F19) * J19*L19)+(G19*H19*I19*J19*N19))</f>
+        <v>16.896</v>
       </c>
       <c r="P19">
         <f>IF(ISBLANK(A19),"",VLOOKUP(A19,$S$14:$T$30,2,FALSE))</f>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Q19">
         <f>IF(ISBLANK(A19), "", O19*P19*$T$10/1000)</f>
-        <v>1.0544371199999999E-4</v>
+        <v>0.00015916032</v>
       </c>
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
@@ -2085,8 +2085,8 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="O20">
-        <f>IF(ISBLANK(A20),"", (G20*H20*(1 - D20 - F20) * J20*L20)+(G20*H20*I20*J20*N20))</f>
-        <v>16.073499999999996</v>
+        <f>IF(ISBLANK(A20),"", (G20*H20*(1 - IF(ISNUMBER(VLOOKUP($B20, $S$22:$AA$39, 8, FALSE)), D20, 0) - F20) * J20*L20)+(G20*H20*I20*J20*N20))</f>
+        <v>21.1735</v>
       </c>
       <c r="P20">
         <f>IF(ISBLANK(A20),"",VLOOKUP(A20,$S$14:$T$30,2,FALSE))</f>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Q20">
         <f>IF(ISBLANK(A20), "", O20*P20*$T$10/1000)</f>
-        <v>1.5141236999999995E-4</v>
+        <v>0.00019945437000000002</v>
       </c>
       <c r="S20" s="2" t="s">
         <v>15</v>
